--- a/dadaia_workspace/public/data/repos.xlsx
+++ b/dadaia_workspace/public/data/repos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,85 +436,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dadaia-workspace</t>
+          <t>example-service</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://github.com/marcoaureliomenezes/dadaia-workspace.git</t>
+          <t>https://github.com/your-org/example-service.git</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLI e lib do dadaia workspace</t>
+          <t>Example backend service</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dadaia-agents</t>
+          <t>example-web</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://github.com/marcoaureliomenezes/dadaia-agents.git</t>
+          <t>https://github.com/your-org/example-web.git</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Agentes AI especializados</t>
+          <t>Example web frontend</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>portifolio</t>
+          <t>example-lib</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://github.com/marcoaureliomenezes/portifolio.git</t>
+          <t>https://github.com/your-org/example-lib.git</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portfólio pessoal</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>tauan-games</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://github.com/marcoaureliomenezes/tauan-games.git</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Projeto de jogos</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>workflow-tools</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://github.com/marcoaureliomenezes/workflow-tools.git</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ferramentas de workflow</t>
+          <t>Example shared library</t>
         </is>
       </c>
     </row>
